--- a/Upwork_Templates/2. Expense_Tracker.xlsx
+++ b/Upwork_Templates/2. Expense_Tracker.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvipi\Desktop\VIP_GitHub\Excel_Projects\Upwork_Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF40E85-CC81-4040-89AE-D7E4FF3821E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C7C141-6F9A-4030-A26B-6685F82A92DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0162D6F0-69B6-47FD-93E3-303CFAE6E4D8}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Expense_Tracker" sheetId="1" r:id="rId1"/>
     <sheet name="description" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>

--- a/Upwork_Templates/2. Expense_Tracker.xlsx
+++ b/Upwork_Templates/2. Expense_Tracker.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvipi\Desktop\VIP_GitHub\Excel_Projects\Upwork_Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C7C141-6F9A-4030-A26B-6685F82A92DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{962C5FC5-EA26-46DC-A3A9-04125F900CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0162D6F0-69B6-47FD-93E3-303CFAE6E4D8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{0162D6F0-69B6-47FD-93E3-303CFAE6E4D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Expense_Tracker" sheetId="1" r:id="rId1"/>
-    <sheet name="description" sheetId="2" r:id="rId2"/>
+    <sheet name="data" sheetId="3" r:id="rId2"/>
+    <sheet name="description" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,9 +38,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Expense Tracker</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Payment Method</t>
+  </si>
+  <si>
+    <t>Mandate</t>
   </si>
 </sst>
 </file>
@@ -618,6 +634,36 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86AB8AF7-FBE8-49E0-87DC-0FA05B3590E6}">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90EE0AC1-9D81-4F30-B4BE-FCEE4D085E8E}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/Upwork_Templates/2. Expense_Tracker.xlsx
+++ b/Upwork_Templates/2. Expense_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvipi\Desktop\VIP_GitHub\Excel_Projects\Upwork_Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{962C5FC5-EA26-46DC-A3A9-04125F900CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{652527B0-7C93-4B44-BB89-EE6667FA2CE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{0162D6F0-69B6-47FD-93E3-303CFAE6E4D8}"/>
   </bookViews>
